--- a/config/Excel/Zones.xlsx
+++ b/config/Excel/Zones.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\MyGame\Idle-RPG\claude\config\Excel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\alway\AppData\Local\Temp\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9E870A67-15FC-4A88-9B5B-8D7EA09D2937}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A266BC42-0C21-4751-BC8C-8638C251D07C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1152" yWindow="1152" windowWidth="17280" windowHeight="8880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="地圖" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="127" uniqueCount="81">
   <si>
     <t>順序</t>
   </si>
@@ -92,19 +92,10 @@
     <t>3</t>
   </si>
   <si>
-    <t>swamp</t>
-  </si>
-  <si>
-    <t>沼澤</t>
-  </si>
-  <si>
     <t>4</t>
   </si>
   <si>
     <t>undead_mountains</t>
-  </si>
-  <si>
-    <t>亡靈山脈</t>
   </si>
   <si>
     <t>5</t>
@@ -142,6 +133,161 @@
   <si>
     <t>冰原</t>
     <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>100</t>
+  </si>
+  <si>
+    <t>150</t>
+  </si>
+  <si>
+    <t>mist_forest</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>迷霧森林</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>200</t>
+  </si>
+  <si>
+    <t>4.5</t>
+  </si>
+  <si>
+    <t>1.45</t>
+  </si>
+  <si>
+    <t>1.3</t>
+  </si>
+  <si>
+    <t>lava_mountain</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>熔岩山</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>250</t>
+  </si>
+  <si>
+    <t>5.5</t>
+  </si>
+  <si>
+    <t>2.6</t>
+  </si>
+  <si>
+    <t>1.5</t>
+  </si>
+  <si>
+    <t>1.4</t>
+  </si>
+  <si>
+    <t>swamp</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>月影沼澤</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>human</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>300</t>
+  </si>
+  <si>
+    <t>0</t>
+  </si>
+  <si>
+    <t>10</t>
+  </si>
+  <si>
+    <t>3.2</t>
+  </si>
+  <si>
+    <t>1.6</t>
+  </si>
+  <si>
+    <t>thunder_peak</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>落雷峰</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>350</t>
+  </si>
+  <si>
+    <t>12</t>
+  </si>
+  <si>
+    <t>24</t>
+  </si>
+  <si>
+    <t>1.7</t>
+  </si>
+  <si>
+    <t>1.85</t>
+  </si>
+  <si>
+    <t>undead_mountains</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>亡靈山脈</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>400</t>
+  </si>
+  <si>
+    <t>20</t>
+  </si>
+  <si>
+    <t>50</t>
+  </si>
+  <si>
+    <t>1.8</t>
+  </si>
+  <si>
+    <t>2.25</t>
+  </si>
+  <si>
+    <t>8</t>
+  </si>
+  <si>
+    <t>450</t>
+  </si>
+  <si>
+    <t>11</t>
+  </si>
+  <si>
+    <t>25</t>
+  </si>
+  <si>
+    <t>9</t>
+  </si>
+  <si>
+    <t>500</t>
+  </si>
+  <si>
+    <t>1000</t>
+  </si>
+  <si>
+    <t>2.2000000000000002</t>
+  </si>
+  <si>
+    <t>600</t>
+  </si>
+  <si>
+    <t>8000</t>
+  </si>
+  <si>
+    <t>2.5</t>
   </si>
 </sst>
 </file>
@@ -151,7 +297,7 @@
   <numFmts count="1">
     <numFmt numFmtId="176" formatCode="0.0"/>
   </numFmts>
-  <fonts count="5">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <name val="Carlito"/>
@@ -192,7 +338,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -215,12 +361,41 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FFD9E2F3"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFD9E2F3"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFD9E2F3"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFD9E2F3"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -240,12 +415,48 @@
     <xf numFmtId="176" fontId="0" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="1" xr:uid="{00000000-0005-0000-0000-000000000000}"/>
     <cellStyle name="一般" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="8">
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border outline="0">
+        <left style="thin">
+          <color rgb="FFD9E2F3"/>
+        </left>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border outline="0">
+        <left style="thin">
+          <color rgb="FFD9E2F3"/>
+        </left>
+        <right style="thin">
+          <color rgb="FFD9E2F3"/>
+        </right>
+      </border>
+    </dxf>
     <dxf>
       <numFmt numFmtId="176" formatCode="0.0"/>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
@@ -267,25 +478,6 @@
         <right style="thin">
           <color rgb="FFD9E2F3"/>
         </right>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border outline="0">
-        <left style="thin">
-          <color rgb="FFD9E2F3"/>
-        </left>
-        <right style="thin">
-          <color rgb="FFD9E2F3"/>
-        </right>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border outline="0">
-        <left style="thin">
-          <color rgb="FFD9E2F3"/>
-        </left>
       </border>
     </dxf>
     <dxf>
@@ -339,7 +531,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="ZonesTable" displayName="ZonesTable" ref="A1:M8" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="ZonesTable" displayName="ZonesTable" ref="A1:M11" totalsRowShown="0">
   <tableColumns count="13">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="順序"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="地圖識別碼"/>
@@ -350,10 +542,10 @@
     <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="前置通關關卡" dataDxfId="6"/>
     <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="最低轉生次數" dataDxfId="5"/>
     <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="生命倍率" dataDxfId="4"/>
-    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0000-00000A000000}" name="攻擊倍率" dataDxfId="2"/>
-    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0000-00000B000000}" name="防禦倍率" dataDxfId="0"/>
+    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0000-00000A000000}" name="攻擊倍率" dataDxfId="3"/>
+    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0000-00000B000000}" name="防禦倍率" dataDxfId="2"/>
     <tableColumn id="12" xr3:uid="{00000000-0010-0000-0000-00000C000000}" name="攻速倍率" dataDxfId="1"/>
-    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0000-00000D000000}" name="經驗金幣獎勵倍率" dataDxfId="3"/>
+    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0000-00000D000000}" name="經驗金幣獎勵倍率" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -554,8 +746,8 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M8"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <dimension ref="A1:M11"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
     <col min="2" max="2" width="20" customWidth="1"/>
@@ -569,7 +761,7 @@
     <col min="13" max="13" width="20" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="26.45" customHeight="1">
+    <row r="1" spans="1:13" ht="26.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -610,7 +802,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="2" spans="1:13" ht="15" customHeight="1">
+    <row r="2" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="3" t="s">
         <v>13</v>
       </c>
@@ -623,8 +815,8 @@
       <c r="D2" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="E2" s="2">
-        <v>200</v>
+      <c r="E2" s="7" t="s">
+        <v>33</v>
       </c>
       <c r="F2" s="2"/>
       <c r="G2" s="4"/>
@@ -647,27 +839,27 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:13" ht="15" customHeight="1">
+    <row r="3" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
         <v>15</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="D3" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="E3" s="2">
-        <v>300</v>
+      <c r="E3" s="7" t="s">
+        <v>34</v>
       </c>
       <c r="F3" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="G3" s="4">
-        <v>200</v>
+      <c r="G3" s="8" t="s">
+        <v>33</v>
       </c>
       <c r="H3" s="4">
         <v>0</v>
@@ -688,209 +880,332 @@
         <v>1.2</v>
       </c>
     </row>
-    <row r="4" spans="1:13" ht="15" customHeight="1">
+    <row r="4" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="B4" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>20</v>
+      <c r="B4" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="C4" s="7" t="s">
+        <v>36</v>
       </c>
       <c r="D4" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="E4" s="2">
-        <v>400</v>
+      <c r="E4" s="7" t="s">
+        <v>37</v>
       </c>
       <c r="F4" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="G4" s="8" t="s">
         <v>34</v>
-      </c>
-      <c r="G4" s="4">
-        <v>300</v>
       </c>
       <c r="H4" s="4">
         <v>0</v>
       </c>
-      <c r="I4" s="4">
-        <v>7</v>
-      </c>
-      <c r="J4" s="4">
-        <v>10</v>
-      </c>
-      <c r="K4" s="6">
-        <v>3.2</v>
-      </c>
-      <c r="L4" s="4">
-        <v>1.6</v>
-      </c>
-      <c r="M4" s="4">
-        <v>1.5</v>
+      <c r="I4" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="J4" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="K4" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="L4" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="M4" s="8" t="s">
+        <v>40</v>
       </c>
     </row>
-    <row r="5" spans="1:13" ht="15" customHeight="1">
+    <row r="5" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>23</v>
+        <v>19</v>
+      </c>
+      <c r="B5" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="C5" s="7" t="s">
+        <v>42</v>
       </c>
       <c r="D5" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="E5" s="2">
-        <v>500</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="G5" s="4">
-        <v>400</v>
+      <c r="E5" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="F5" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="G5" s="8" t="s">
+        <v>37</v>
       </c>
       <c r="H5" s="4">
         <v>0</v>
       </c>
-      <c r="I5" s="4">
+      <c r="I5" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="J5" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="K5" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="L5" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="M5" s="8" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="B6" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="C6" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="D6" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="E6" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="F6" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="G6" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="H6" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="I6" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="J6" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="K6" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="L6" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="M6" s="8" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="B7" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="C7" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="D7" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="E7" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="F7" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="G7" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="H7" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="I7" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="J7" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="K7" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="L7" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="M7" s="8" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="B8" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="C8" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="D8" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="E8" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="F8" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="G8" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="H8" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="I8" s="8" t="s">
+        <v>66</v>
+      </c>
+      <c r="J8" s="8" t="s">
+        <v>67</v>
+      </c>
+      <c r="K8" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="L8" s="8" t="s">
+        <v>68</v>
+      </c>
+      <c r="M8" s="8" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A9" s="9" t="s">
+        <v>70</v>
+      </c>
+      <c r="B9" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="C9" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="D9" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="E9" s="9" t="s">
+        <v>71</v>
+      </c>
+      <c r="F9" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="J5" s="4">
-        <v>50</v>
-      </c>
-      <c r="K5" s="6">
-        <v>10</v>
-      </c>
-      <c r="L5" s="4">
-        <v>1.8</v>
-      </c>
-      <c r="M5" s="4">
-        <v>2.25</v>
+      <c r="G9" s="11" t="s">
+        <v>65</v>
+      </c>
+      <c r="H9" s="12" t="s">
+        <v>72</v>
+      </c>
+      <c r="I9" s="12" t="s">
+        <v>67</v>
+      </c>
+      <c r="J9" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="K9" s="12" t="s">
+        <v>73</v>
+      </c>
+      <c r="L9" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="M9" s="13" t="s">
+        <v>19</v>
       </c>
     </row>
-    <row r="6" spans="1:13" ht="15" customHeight="1">
-      <c r="A6" s="3" t="s">
+    <row r="10" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A10" s="9" t="s">
+        <v>74</v>
+      </c>
+      <c r="B10" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="C10" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="D10" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="B6" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="C6" s="2" t="s">
+      <c r="E10" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="F10" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="G10" s="11" t="s">
+        <v>71</v>
+      </c>
+      <c r="H10" s="12" t="s">
+        <v>72</v>
+      </c>
+      <c r="I10" s="12" t="s">
+        <v>34</v>
+      </c>
+      <c r="J10" s="12" t="s">
+        <v>76</v>
+      </c>
+      <c r="K10" s="12" t="s">
+        <v>67</v>
+      </c>
+      <c r="L10" s="12" t="s">
+        <v>77</v>
+      </c>
+      <c r="M10" s="13" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A11" s="9" t="s">
+        <v>53</v>
+      </c>
+      <c r="B11" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="C11" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="D11" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="E11" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="F11" s="10" t="s">
         <v>26</v>
       </c>
-      <c r="D6" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="E6" s="2">
-        <v>600</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="G6" s="4">
-        <v>500</v>
-      </c>
-      <c r="H6" s="4">
-        <v>11</v>
-      </c>
-      <c r="I6" s="4">
-        <v>50</v>
-      </c>
-      <c r="J6" s="4">
-        <v>200</v>
-      </c>
-      <c r="K6" s="6">
-        <v>25</v>
-      </c>
-      <c r="L6" s="4">
-        <v>2</v>
-      </c>
-      <c r="M6" s="4">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13" ht="15" customHeight="1">
-      <c r="A7" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="E7" s="2">
-        <v>700</v>
-      </c>
-      <c r="F7" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="G7" s="4">
-        <v>600</v>
-      </c>
-      <c r="H7" s="4">
-        <v>11</v>
-      </c>
-      <c r="I7" s="4">
-        <v>150</v>
-      </c>
-      <c r="J7" s="4">
-        <v>1000</v>
-      </c>
-      <c r="K7" s="6">
-        <v>50</v>
-      </c>
-      <c r="L7" s="4">
-        <v>2.2000000000000002</v>
-      </c>
-      <c r="M7" s="4">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13" ht="15" customHeight="1">
-      <c r="A8" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="C8" s="2" t="s">
+      <c r="G11" s="11" t="s">
+        <v>75</v>
+      </c>
+      <c r="H11" s="12" t="s">
+        <v>72</v>
+      </c>
+      <c r="I11" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="J11" s="12" t="s">
+        <v>79</v>
+      </c>
+      <c r="K11" s="12" t="s">
         <v>33</v>
       </c>
-      <c r="D8" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="E8" s="2">
-        <v>800</v>
-      </c>
-      <c r="F8" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="G8" s="4">
-        <v>700</v>
-      </c>
-      <c r="H8" s="4">
-        <v>11</v>
-      </c>
-      <c r="I8" s="4">
-        <v>500</v>
-      </c>
-      <c r="J8" s="4">
-        <v>8000</v>
-      </c>
-      <c r="K8" s="6">
-        <v>100</v>
-      </c>
-      <c r="L8" s="4">
-        <v>2.5</v>
-      </c>
-      <c r="M8" s="4">
-        <v>24</v>
+      <c r="L11" s="12" t="s">
+        <v>80</v>
+      </c>
+      <c r="M11" s="13" t="s">
+        <v>60</v>
       </c>
     </row>
   </sheetData>
